--- a/Results/Consensus_more_than_2/MC/Supplement/Chisq_tests.xlsx
+++ b/Results/Consensus_more_than_2/MC/Supplement/Chisq_tests.xlsx
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Vital status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928336508478266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456510649220862</t>
+    <t xml:space="preserve">0.897433081005182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595625500133369</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -41,94 +41,94 @@
     <t xml:space="preserve">Ethnicity vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752650645932338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20147467294137</t>
+    <t xml:space="preserve">0.79416268457483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0293001238839</t>
   </si>
   <si>
     <t xml:space="preserve">Race vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2719098514469e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3575568914632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125</t>
+    <t xml:space="preserve">7.53412290233141e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4212061937682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118</t>
   </si>
   <si>
     <t xml:space="preserve">Lymph node status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196991182431591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67753012708395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.058</t>
+    <t xml:space="preserve">0.16976842356549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02786006779198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.064</t>
   </si>
   <si>
     <t xml:space="preserve">Histology vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33965998274165e-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.508554344671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.229</t>
+    <t xml:space="preserve">1.68465525051158e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.964524600598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228</t>
   </si>
   <si>
     <t xml:space="preserve">Menopausal status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0925386092228796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9421038906551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.059</t>
+    <t xml:space="preserve">0.102507375153211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6005997897383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
   </si>
   <si>
     <t xml:space="preserve">PR status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2963650742453e-47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.71503161287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
+    <t xml:space="preserve">8.6061733047214e-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">234.447372007701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442</t>
   </si>
   <si>
     <t xml:space="preserve">ER status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54063179737285e-66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.359317048498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721</t>
+    <t xml:space="preserve">3.82184194473258e-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.160059071877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725</t>
   </si>
   <si>
     <t xml:space="preserve">HER2 status vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000119072748760001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2859828289055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127</t>
+    <t xml:space="preserve">5.39569793563486e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2440381541549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132</t>
   </si>
   <si>
     <t xml:space="preserve">Metastasis vs MC cluster</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">Stage vs MC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0120032973113481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1494078911816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081</t>
+    <t xml:space="preserve">0.0104232355631637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5491154018112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.083</t>
   </si>
 </sst>
 </file>
